--- a/output/pdf_financials_xlsx/AIAI.xlsx
+++ b/output/pdf_financials_xlsx/AIAI.xlsx
@@ -498,25 +498,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -525,25 +517,17 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0.000778</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.386085</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.118853</v>
       </c>
     </row>
     <row r="7">
@@ -552,25 +536,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -579,25 +555,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -606,25 +574,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -633,25 +593,17 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -660,25 +612,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0.000778</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.386085</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.118853</v>
       </c>
     </row>
     <row r="12">
@@ -687,25 +631,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -714,25 +650,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -741,25 +669,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -768,25 +688,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.139913</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -795,25 +707,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-2.084568</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.852526</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.733067</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="17">
@@ -822,25 +726,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -903,25 +799,17 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-2.084568</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.852526</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.733067</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="21">
@@ -930,25 +818,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -957,25 +837,17 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -984,25 +856,17 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-2.084568</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.852526</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.733067</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="24">
@@ -1030,25 +894,17 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -1057,10 +913,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>41.69136</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1084,25 +938,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-2.084568</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.852526</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.733067</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="28">
@@ -1114,20 +960,14 @@
       <c r="B28" s="3" t="n">
         <v>0.152622</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1136,25 +976,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.931946</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.852526</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.733067</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="30">
@@ -1163,25 +995,17 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-248322.1079691517</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-284175.3333333334</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-189.8719193959879</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-1106.173171901424</v>
       </c>
     </row>
     <row r="31">
@@ -1190,25 +1014,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1217,25 +1033,17 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-267939.3316195373</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-284175.3333333334</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-189.8719193959879</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-1106.173171901424</v>
       </c>
     </row>
     <row r="33">
@@ -1256,20 +1064,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1304,20 +1106,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.005149</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.533165</v>
       </c>
     </row>
     <row r="37">
@@ -1331,18 +1127,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0.081049</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1356,20 +1148,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1383,20 +1169,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1431,20 +1211,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>0.081729</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.131438</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.129895</v>
       </c>
     </row>
     <row r="42">
@@ -1458,20 +1232,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1485,20 +1253,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1512,20 +1274,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1539,20 +1295,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1566,20 +1316,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1593,20 +1337,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1620,20 +1358,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>1.823147</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.07098500000000001</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1.513735</v>
       </c>
     </row>
     <row r="49">
@@ -1668,20 +1400,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1695,20 +1421,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1722,20 +1442,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1749,20 +1463,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1776,20 +1484,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1830,20 +1532,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1857,20 +1553,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1884,20 +1574,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1911,20 +1595,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1938,20 +1616,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1965,20 +1637,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1992,20 +1658,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2040,20 +1700,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2067,20 +1721,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2094,20 +1742,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2121,20 +1763,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -2169,20 +1805,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2196,20 +1826,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2223,20 +1847,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2271,20 +1889,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2298,20 +1910,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0.023029</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.07519000000000001</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0.038702</v>
       </c>
     </row>
     <row r="75">
@@ -2325,20 +1931,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2373,20 +1973,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2400,20 +1994,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2427,20 +2015,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2481,20 +2063,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2508,20 +2084,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2535,20 +2105,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2562,20 +2126,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2589,20 +2147,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2616,20 +2168,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2664,20 +2210,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>28.815881</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>30.500534</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>39.021723</v>
       </c>
     </row>
     <row r="89">
@@ -2691,20 +2231,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2745,20 +2279,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2793,20 +2321,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2841,20 +2363,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2868,20 +2384,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>1.085466</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.198557</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1.834628</v>
       </c>
     </row>
     <row r="97">
@@ -2918,25 +2428,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-2.084568</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.852526</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.733067</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="100">
@@ -2948,20 +2450,14 @@
       <c r="B100" s="3" t="n">
         <v>0.152622</v>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2971,20 +2467,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.008432</v>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.192211</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.024842</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.081049</v>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08518100000000001</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0.024261</v>
       </c>
     </row>
     <row r="102">
@@ -2993,25 +2485,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3020,25 +2504,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.00449</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.016745</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.00809</v>
       </c>
     </row>
     <row r="104">
@@ -3066,25 +2542,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>-0.038662</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.025203</v>
       </c>
     </row>
     <row r="106">
@@ -3093,25 +2561,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.062766</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.477137</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.178757</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.028989</v>
       </c>
     </row>
     <row r="107">
@@ -3139,25 +2599,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3166,25 +2618,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3193,25 +2637,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3220,25 +2656,17 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -3247,25 +2675,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3274,25 +2694,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3301,25 +2713,17 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3328,25 +2732,17 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3355,25 +2751,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3382,25 +2770,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3409,25 +2789,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3436,25 +2808,19 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>0.476989</v>
       </c>
     </row>
     <row r="120">
@@ -3463,25 +2829,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3490,25 +2848,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3517,25 +2867,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3544,25 +2886,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3571,25 +2905,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3598,25 +2924,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3625,25 +2943,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3679,25 +2989,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3718,7 +3020,7 @@
         <v>1.402699</v>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0.476989</v>
+        <v>-0.003966</v>
       </c>
     </row>
     <row r="130">
@@ -3746,25 +3048,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3811,25 +3105,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3838,25 +3124,17 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.561716</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.958039</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.170122</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-1.098227</v>
       </c>
     </row>
   </sheetData>
@@ -6119,7 +5397,11 @@
           <t>Net loss and comprehensive loss for the period</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -6221,7 +5503,11 @@
           <t>Prepaid expenses</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>-0.00449</v>
       </c>
@@ -6293,7 +5579,11 @@
           <t>Other receivables</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -6361,7 +5651,11 @@
           <t>Deferred revenue 6</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6827,7 +6121,11 @@
           <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -7117,7 +6415,11 @@
           <t>Net Loss and Comprehensive Loss for the Period</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>-2.084568</v>
       </c>
@@ -7339,7 +6641,11 @@
           <t>Other Receivables</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E92" s="5" t="n">
         <v>0.183779</v>
       </c>
@@ -7707,7 +7013,11 @@
           <t>Sales revenue</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -7879,7 +7189,11 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -7915,7 +7229,11 @@
           <t>Net loss and comprehensive loss</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -8229,7 +7547,11 @@
           <t>Net loss for the period - - -</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -8823,7 +8145,11 @@
           <t>Net Loss for The Period - - -</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>-2.084568</v>
       </c>
@@ -9245,7 +8571,11 @@
           <t>Sales Revenue</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="n">
         <v>0.000778</v>
       </c>
@@ -9503,7 +8833,11 @@
           <t>Net (Loss) and Comprehensive (Loss)</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E153" s="5" t="n">
         <v>-2.084568</v>
       </c>

--- a/output/pdf_financials_xlsx/AIAI.xlsx
+++ b/output/pdf_financials_xlsx/AIAI.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/AIAI.xlsx
+++ b/output/pdf_financials_xlsx/AIAI.xlsx
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1. Nature of Operations and Going Concern</t>
+          <t>1.  Nature of Operations and Going Concern</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2. Basis of Presentation</t>
+          <t>2.  Basis of Presentation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1. Nature of Operations and Going Concern</t>
+          <t>1.  Nature of Operations and Going Concern</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">

--- a/output/pdf_financials_xlsx/AIAI.xlsx
+++ b/output/pdf_financials_xlsx/AIAI.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>2.085346</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.992739</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>1.119152</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1.433573</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.000778</v>
+        <v>-2.084568</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.0003</v>
+        <v>-0.992439</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.386085</v>
+        <v>-0.733067</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.118853</v>
+        <v>-1.31472</v>
       </c>
     </row>
     <row r="12">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.77657</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.059753</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.496749</v>
       </c>
     </row>
     <row r="35">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.005</v>
+        <v>1.78157</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.005149</v>
+        <v>0.064902</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.533165</v>
+        <v>2.029914</v>
       </c>
     </row>
     <row r="37">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.823147</v>
+        <v>0.046577</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07098500000000001</v>
+        <v>0.011232</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.513735</v>
+        <v>0.016986</v>
       </c>
     </row>
     <row r="49">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
